--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484617_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484617_PROCESSED_CHRONO.xlsx
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ORTEGA IBANEZ</t>
+          <t>E. SILVA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8579</v>
+        <v>1.7019</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4258</v>
+        <v>2.0397</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5679</v>
+        <v>-0.3378</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2271</v>
+        <v>-1.0687</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1663</v>
+        <v>-0.6392</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0608</v>
+        <v>-0.4295</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3752</v>
+        <v>0.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.282</v>
+        <v>0.1484</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0515</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1481</v>
+        <v>-1.2686</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.1157</v>
+        <v>-0.7876</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0324</v>
+        <v>-0.481</v>
       </c>
       <c r="P3" t="n">
-        <v>-4.7647</v>
+        <v>0.9163</v>
       </c>
       <c r="Q3" t="n">
-        <v>-6.7805</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0158</v>
+        <v>0.9163</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5967</v>
+        <v>-0.0462</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0302</v>
+        <v>-0.0607</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4335</v>
+        <v>0.0145</v>
       </c>
       <c r="V3" t="n">
-        <v>3.7988</v>
+        <v>1.9005</v>
       </c>
       <c r="W3" t="n">
-        <v>3.8009</v>
+        <v>1.9005</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. SILVA</t>
+          <t>I. FRANCH RUIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4382</v>
+        <v>0.736</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7513</v>
+        <v>0.2087</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3131</v>
+        <v>0.5274</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.0687</v>
+        <v>0.7005</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6392</v>
+        <v>0.1877</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4295</v>
+        <v>0.5128</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2</v>
+        <v>0.1084</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1484</v>
+        <v>0.1084</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0515</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2686</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7876</v>
+        <v>0.0793</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.481</v>
+        <v>0.5128</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9163</v>
+        <v>0.1833</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9163</v>
+        <v>0.1833</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3099</v>
+        <v>0.1742</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3492</v>
+        <v>0.1003</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0393</v>
+        <v>0.07389999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>1.9005</v>
+        <v>-0.3219</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9005</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. FRANCH RUIZ</t>
+          <t>P. BAENA SÁNCHEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5437</v>
+        <v>0.3251</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0164</v>
+        <v>0.3251</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5274</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7005</v>
+        <v>0.3251</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1877</v>
+        <v>0.3251</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5128</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1084</v>
+        <v>0.3251</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1084</v>
+        <v>0.3251</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5921999999999999</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0793</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5128</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0181</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.092</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.07389999999999999</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. BAENA SÁNCHEZ</t>
+          <t>J. BERMEJO DORRONSORO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3251</v>
+        <v>0.234</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3251</v>
+        <v>1.2494</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-1.0154</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3251</v>
+        <v>-0.061</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3251</v>
+        <v>-1.7086</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.6476</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3251</v>
+        <v>1.4244</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3251</v>
+        <v>-0.576</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.0004</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-1.4854</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-1.1326</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.3528</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.0158</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.0158</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0.4538</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-0.175</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0.2789</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BERMEJO DORRONSORO</t>
+          <t>A. ORTEGA IBANEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0876</v>
+        <v>0.1877</v>
       </c>
       <c r="E7" t="n">
-        <v>1.002</v>
+        <v>0.8051</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0897</v>
+        <v>-0.6173999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.061</v>
+        <v>1.2271</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7086</v>
+        <v>1.1663</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6476</v>
+        <v>0.0608</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4244</v>
+        <v>3.3752</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.576</v>
+        <v>3.282</v>
       </c>
       <c r="L7" t="n">
-        <v>2.0004</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4854</v>
+        <v>-2.1481</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1326</v>
+        <v>-2.1157</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3528</v>
+        <v>-0.0324</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0158</v>
+        <v>-4.7647</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-6.7805</v>
       </c>
       <c r="R7" t="n">
         <v>2.0158</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7755</v>
+        <v>-0.0735</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4223</v>
+        <v>0.4095</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3532</v>
+        <v>-0.4831</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.267</v>
+        <v>3.7988</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.8009</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.267</v>
+        <v>-0.0021</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7111</v>
+        <v>-0.2437</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4161</v>
+        <v>-0.0726</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.295</v>
+        <v>-0.1711</v>
       </c>
       <c r="G8" t="n">
         <v>0.113</v>
@@ -1078,13 +1078,13 @@
         <v>1.8326</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8345</v>
+        <v>-0.3671</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4412</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3933</v>
+        <v>-0.2694</v>
       </c>
       <c r="V8" t="n">
         <v>0.0104</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.039</v>
+        <v>-0.984</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1218</v>
+        <v>-0.0668</v>
       </c>
       <c r="F9" t="n">
         <v>-0.9172</v>
@@ -1156,10 +1156,10 @@
         <v>0.1833</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2383</v>
+        <v>-0.1833</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1652</v>
+        <v>-0.1101</v>
       </c>
       <c r="U9" t="n">
         <v>-0.0732</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8393</v>
+        <v>-2.1226</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9907</v>
+        <v>-0.9768</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8486</v>
+        <v>-1.1459</v>
       </c>
       <c r="G10" t="n">
         <v>-4.4384</v>
@@ -1234,13 +1234,13 @@
         <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6371</v>
+        <v>-0.9204</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3869</v>
+        <v>-0.3729</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2503</v>
+        <v>-0.5475</v>
       </c>
       <c r="V10" t="n">
         <v>1.5868</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4822</v>
+        <v>-2.3365</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2655</v>
+        <v>-2.1693</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2168</v>
+        <v>-0.1672</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9836</v>
@@ -1312,13 +1312,13 @@
         <v>0.9163</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4986</v>
+        <v>-0.3529</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2572</v>
+        <v>-0.161</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2415</v>
+        <v>-0.1919</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8942</v>
+        <v>-4.5229</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1134</v>
+        <v>-2.866</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7808</v>
+        <v>-1.6569</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1994</v>
@@ -1390,13 +1390,13 @@
         <v>0.9163</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4936</v>
+        <v>-1.1224</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9359</v>
+        <v>-0.6885</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5577</v>
+        <v>-0.4338</v>
       </c>
       <c r="V12" t="n">
         <v>-0.0021</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. BERENGUER CASCO</t>
+          <t>P. BAENA SANCHEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.931</v>
+        <v>-4.8013</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2918</v>
+        <v>-4.4181</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.6392</v>
+        <v>-0.3833</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.0016</v>
+        <v>-6.2694</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.5495</v>
+        <v>-1.4485</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4521</v>
+        <v>-4.8209</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6502</v>
+        <v>-3.8528</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5570000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09320000000000001</v>
+        <v>-3.7628</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.6517</v>
+        <v>-2.4166</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.1065</v>
+        <v>-1.3585</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5452</v>
+        <v>-1.0581</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.4661</v>
+        <v>2.1991</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.9321</v>
+        <v>-0.1833</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4661</v>
+        <v>2.3823</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5183</v>
+        <v>-0.4174</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3318</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1865</v>
+        <v>-0.3469</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.945</v>
+        <v>-0.3136</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3219</v>
+        <v>-0.3115</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.267</v>
+        <v>-0.0021</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. BAENA SANCHEZ</t>
+          <t>M. BERENGUER CASCO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.183</v>
+        <v>-5.0904</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.8988</v>
+        <v>-2.2778</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2842</v>
+        <v>-2.8126</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.2694</v>
+        <v>-2.0016</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4485</v>
+        <v>-1.5495</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.8209</v>
+        <v>-0.4521</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.8528</v>
+        <v>0.6502</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.09</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.7628</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4166</v>
+        <v>-2.6517</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3585</v>
+        <v>-2.1065</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.0581</v>
+        <v>-0.5452</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1991</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1833</v>
+        <v>-2.9321</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3823</v>
+        <v>1.4661</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7991</v>
+        <v>-0.6778</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5513</v>
+        <v>-0.3179</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2478</v>
+        <v>-0.3599</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3136</v>
+        <v>-0.945</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3115</v>
+        <v>0.3219</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.0021</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.5764</v>
+        <v>-5.1116</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.4975</v>
+        <v>-1.3052</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.0789</v>
+        <v>-3.8064</v>
       </c>
       <c r="G15" t="n">
         <v>-0.7476</v>
@@ -1624,13 +1624,13 @@
         <v>0.733</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.4314</v>
+        <v>-0.9666</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7707000000000001</v>
+        <v>-0.5784</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6607</v>
+        <v>-0.3882</v>
       </c>
       <c r="V15" t="n">
         <v>-2.8476</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-20.0282</v>
+        <v>-19.4776</v>
       </c>
       <c r="E16" t="n">
-        <v>-7.5243</v>
+        <v>-6.9739</v>
       </c>
       <c r="F16" t="n">
-        <v>-12.504</v>
+        <v>-12.5038</v>
       </c>
       <c r="G16" t="n">
         <v>-13.8373</v>
@@ -1702,22 +1702,22 @@
         <v>15.5769</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.9577</v>
+        <v>-5.4072</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.6735</v>
+        <v>-2.1228</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.2845</v>
+        <v>-3.2844</v>
       </c>
       <c r="V16" t="n">
         <v>1.599299999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>7.633</v>
+        <v>7.633000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-6.033799999999999</v>
+        <v>-6.0338</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>10.2492</v>
+        <v>11.8883</v>
       </c>
       <c r="E17" t="n">
-        <v>8.26</v>
+        <v>9.221500000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9892</v>
+        <v>2.6667</v>
       </c>
       <c r="G17" t="n">
         <v>5.6652</v>
@@ -1780,13 +1780,13 @@
         <v>3.1154</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1491</v>
+        <v>0.49</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7896</v>
+        <v>0.172</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3595</v>
+        <v>0.318</v>
       </c>
       <c r="V17" t="n">
         <v>3.1674</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.5429</v>
+        <v>6.5705</v>
       </c>
       <c r="E18" t="n">
-        <v>4.6206</v>
+        <v>4.8129</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9223</v>
+        <v>1.7576</v>
       </c>
       <c r="G18" t="n">
         <v>5.4844</v>
@@ -1858,13 +1858,13 @@
         <v>2.5656</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1031</v>
+        <v>2.1306</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8409</v>
+        <v>1.0332</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2622</v>
+        <v>1.0974</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3115</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.4097</v>
+        <v>3.2519</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7958</v>
+        <v>3.0843</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3861</v>
+        <v>0.1676</v>
       </c>
       <c r="G19" t="n">
         <v>4.1752</v>
@@ -1936,13 +1936,13 @@
         <v>0.3665</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5718</v>
+        <v>0.2704</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.129</v>
+        <v>0.1595</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4428</v>
+        <v>0.1108</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6439</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1887</v>
+        <v>2.0527</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3995</v>
+        <v>0.7841</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7892</v>
+        <v>1.2686</v>
       </c>
       <c r="G20" t="n">
         <v>-0.2269</v>
@@ -2014,13 +2014,13 @@
         <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7675999999999999</v>
+        <v>0.0963</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4774</v>
+        <v>-0.0927</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2903</v>
+        <v>0.1891</v>
       </c>
       <c r="V20" t="n">
         <v>1.267</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9183</v>
+        <v>1.2957</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0117</v>
+        <v>0.0844</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9301</v>
+        <v>1.2112</v>
       </c>
       <c r="G21" t="n">
         <v>1.472</v>
@@ -2092,13 +2092,13 @@
         <v>1.8326</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3468</v>
+        <v>0.7242</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0355</v>
+        <v>0.1316</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3114</v>
+        <v>0.5926</v>
       </c>
       <c r="V21" t="n">
         <v>-1.267</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. AZNAR MARTINEZ</t>
+          <t>K. MONTAÑO LINARES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9095</v>
+        <v>0.6502</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6996</v>
+        <v>0.6502</v>
       </c>
       <c r="F22" t="n">
-        <v>1.6091</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>1.9791</v>
+        <v>0.6502</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2677</v>
+        <v>0.6502</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7113</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1.7581</v>
+        <v>0.6502</v>
       </c>
       <c r="K22" t="n">
-        <v>1.5914</v>
+        <v>0.6502</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1667</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.221</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3237</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5446</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.5656</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.0317</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4661</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.7629</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5739</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.189</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. MATE SEBASTIA</t>
+          <t>M. PAÑOS HUERTAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.6251</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3406</v>
+        <v>0.6251</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5127</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4771</v>
+        <v>0.6251</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.0156</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.5385</v>
+        <v>0.6251</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3901</v>
+        <v>0.6251</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2236</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8335</v>
+        <v>0.6251</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.087</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.792</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.705</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.8326</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.1833</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.0158</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.3878</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.537</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8509</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.89</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.6231</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>K. MONTAÑO LINARES</t>
+          <t>C. TATO SAPENA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6502</v>
+        <v>0.1222</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6502</v>
+        <v>-0.0551</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.1773</v>
       </c>
       <c r="G24" t="n">
-        <v>0.6502</v>
+        <v>-0.0885</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6502</v>
+        <v>-0.2167</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>0.1282</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6502</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6502</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>-0.0885</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>-0.2167</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>0.1282</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>0.0275</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>-0.0551</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M. PAÑOS HUERTAS</t>
+          <t>J. MATE SEBASTIA</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6251</v>
+        <v>-0.0137</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6251</v>
+        <v>-0.3325</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.3189</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6251</v>
+        <v>-1.4771</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>-3.0156</v>
       </c>
       <c r="I25" t="n">
-        <v>0.6251</v>
+        <v>1.5385</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6251</v>
+        <v>-0.3901</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>-1.2236</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6251</v>
+        <v>0.8335</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>-1.087</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>0.705</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.8326</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-0.1833</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.0158</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.5209</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>0.8639</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>0.657</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>-1.89</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.6231</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>C. TATO SAPENA</t>
+          <t>A. MARTIN MARGARIT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,73 +2437,73 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0727</v>
+        <v>-0.0443</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.0551</v>
+        <v>1.4787</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1278</v>
+        <v>-1.5231</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.0885</v>
+        <v>1.1153</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2167</v>
+        <v>1.0962</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1282</v>
+        <v>0.0191</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2.2725</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>2.1891</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>0.0833</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0885</v>
+        <v>-1.1572</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.2167</v>
+        <v>-1.0929</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1282</v>
+        <v>-0.0643</v>
       </c>
       <c r="P26" t="n">
-        <v>0.1833</v>
+        <v>0.733</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R26" t="n">
-        <v>0.1833</v>
+        <v>1.6493</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.022</v>
+        <v>0.3298</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.0551</v>
+        <v>0.1226</v>
       </c>
       <c r="U26" t="n">
-        <v>0.033</v>
+        <v>0.2072</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>-2.2224</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A. MARTIN MARGARIT</t>
+          <t>A. AZNAR MARTINEZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.027</v>
+        <v>-0.2402</v>
       </c>
       <c r="E27" t="n">
-        <v>1.5749</v>
+        <v>-1.565</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.5478</v>
+        <v>1.3248</v>
       </c>
       <c r="G27" t="n">
-        <v>1.1153</v>
+        <v>1.9791</v>
       </c>
       <c r="H27" t="n">
-        <v>1.0962</v>
+        <v>1.2677</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0191</v>
+        <v>0.7113</v>
       </c>
       <c r="J27" t="n">
-        <v>2.2725</v>
+        <v>1.7581</v>
       </c>
       <c r="K27" t="n">
-        <v>2.1891</v>
+        <v>1.5914</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0833</v>
+        <v>0.1667</v>
       </c>
       <c r="M27" t="n">
-        <v>-1.1572</v>
+        <v>0.221</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.0929</v>
+        <v>-0.3237</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.0643</v>
+        <v>0.5446</v>
       </c>
       <c r="P27" t="n">
-        <v>0.733</v>
+        <v>-2.5656</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.9163</v>
+        <v>-4.0317</v>
       </c>
       <c r="R27" t="n">
-        <v>1.6493</v>
+        <v>1.4661</v>
       </c>
       <c r="S27" t="n">
-        <v>0.4011</v>
+        <v>1.6133</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2187</v>
+        <v>0.7085</v>
       </c>
       <c r="U27" t="n">
-        <v>0.1824</v>
+        <v>0.9048</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.2224</v>
+        <v>-1.267</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>-2.2224</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="28">
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.7591</v>
+        <v>-0.4109</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.0206</v>
+        <v>-0.9244</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2615</v>
+        <v>0.5135</v>
       </c>
       <c r="G28" t="n">
         <v>-0.1818</v>
@@ -2638,13 +2638,13 @@
         <v>0.733</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.394</v>
+        <v>-0.0458</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.2202</v>
+        <v>-0.1241</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.1738</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.2919</v>
+        <v>-1.3663</v>
       </c>
       <c r="E29" t="n">
         <v>-1.6124</v>
       </c>
       <c r="F29" t="n">
-        <v>0.3204</v>
+        <v>0.2461</v>
       </c>
       <c r="G29" t="n">
         <v>-0.7296</v>
@@ -2716,13 +2716,13 @@
         <v>0.1833</v>
       </c>
       <c r="S29" t="n">
-        <v>0.1707</v>
+        <v>0.0963</v>
       </c>
       <c r="T29" t="n">
         <v>-0.0551</v>
       </c>
       <c r="U29" t="n">
-        <v>0.2257</v>
+        <v>0.1514</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-2.3675</v>
+        <v>-2.4301</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.3635</v>
+        <v>-3.7482</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9961</v>
+        <v>1.3181</v>
       </c>
       <c r="G30" t="n">
         <v>-4.6254</v>
@@ -2794,13 +2794,13 @@
         <v>2.0158</v>
       </c>
       <c r="S30" t="n">
-        <v>0.6898</v>
+        <v>0.6273</v>
       </c>
       <c r="T30" t="n">
-        <v>0.8047</v>
+        <v>0.4201</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.1149</v>
+        <v>0.2072</v>
       </c>
       <c r="V30" t="n">
         <v>1.5681</v>
@@ -2827,13 +2827,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>20.0281</v>
+        <v>21.9511</v>
       </c>
       <c r="E31" t="n">
-        <v>12.5038</v>
+        <v>12.5036</v>
       </c>
       <c r="F31" t="n">
-        <v>7.524500000000001</v>
+        <v>9.447299999999998</v>
       </c>
       <c r="G31" t="n">
         <v>13.8372</v>
@@ -2842,7 +2842,7 @@
         <v>5.0218</v>
       </c>
       <c r="I31" t="n">
-        <v>8.815099999999999</v>
+        <v>8.815099999999997</v>
       </c>
       <c r="J31" t="n">
         <v>18.7625</v>
@@ -2872,22 +2872,22 @@
         <v>17.4095</v>
       </c>
       <c r="S31" t="n">
-        <v>5.957700000000001</v>
+        <v>7.880799999999999</v>
       </c>
       <c r="T31" t="n">
-        <v>3.2843</v>
+        <v>3.2844</v>
       </c>
       <c r="U31" t="n">
-        <v>2.6733</v>
+        <v>4.5963</v>
       </c>
       <c r="V31" t="n">
-        <v>-1.599299999999999</v>
+        <v>-1.5993</v>
       </c>
       <c r="W31" t="n">
         <v>6.0337</v>
       </c>
       <c r="X31" t="n">
-        <v>-7.6332</v>
+        <v>-7.633199999999999</v>
       </c>
     </row>
   </sheetData>
